--- a/healthcare_surveys/004_digital_health_literacy_survey--healthcare_surveys.xlsx
+++ b/healthcare_surveys/004_digital_health_literacy_survey--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>What is your zip code?</t>
+          <t>Question Thirteen</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>What is the zip code of your city?</t>
+          <t>Question Fifteen</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>How many years do you have?</t>
+          <t>Question Seventeen</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>What is your zip code?</t>
+          <t>Question Eighteen</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>How many children do you have?</t>
+          <t>Question Twenty One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>What is your email?</t>
+          <t>Question Twenty Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>What is your age?</t>
+          <t>Question Twenty Three</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>How many kids do you have?</t>
+          <t>Question Twenty Four</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
